--- a/samples/output_auditoria_mock.xlsx
+++ b/samples/output_auditoria_mock.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auditoría" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,10 +27,9 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -39,27 +38,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0090EE90"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFA500"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF6B6B"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,15 +67,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,343 +442,589 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Reserva CB</t>
+          <t>Usuario</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Huésped</t>
+          <t>Fecha y hora</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Hab.</t>
+          <t>Habitación</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Comprobante SF</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Monto CB</t>
+          <t>Apellido</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Monto SF</t>
+          <t>Núm. de reserva</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Diferencia</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Observación</t>
+          <t>Crédito</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TC</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>FACTURA N°</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RES-10041</t>
+          <t>System</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Rodríguez, Carlos</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
+          <t>06/03/2026 23:10</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>FA-0001-00010041</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>85000</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>85000</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
+          <t>Carlos</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1001001001001</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>VISA_CREDITO - Pago Registrada</t>
+        </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr"/>
+          <t>$85.000/TC 1420/VISA CREDITO 4134/CUPON 8801/LOTE 100</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>59.86</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1.419,98</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>$ 85.000,00</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>1-1001</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ REFACTURAR: PV incorrecto (1), debería ser 14</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RES-10042</t>
+          <t>System</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>López, María</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
+          <t>06/03/2026 23:15</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>302</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>FB-0001-00010042</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>120000</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Lopez</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2002002002002</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA - Pago Registrada</t>
+        </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>$120.000 TC 1420 TRANSFERENCIA</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>1.420,12</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>$ 120.000,00</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>1-1002</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ REFACTURAR: PV incorrecto (1), debería ser 14</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>RES-10043</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Smith, John</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>FT-0001-00010043</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>110250</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>110250</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>MATCH GREEN_CARD</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>USD 75 x TC 1470</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>06/03/2026 23:20</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3003003003003</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>GREEN_CARD - Pago Registrada</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>$110.250 TC 1470 E4HOTELS</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>1.470,00</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>$ 110.250,00</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>FX</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>1-1003</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>OK (Factura X - GREEN_CARD/USD)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>RES-10044</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Martínez, Ana</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>FB-0001-00010044</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>MATCH (2 pagos)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Pago dividido en 2 transacciones CB</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06/03/2026 23:25</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>410</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>4004004004004</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MASTERCARD - Pago Registrada</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$45.000/TC 1420/MASTER 5678/CUPON 8802/LOTE 100</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.420,01</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>$ 45.000,00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1-1004</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>✅ Pago parcial 1/2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>RES-10045</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Gómez, Pedro</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>ANULACIÓN LIFO</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>Par pago/anulación excluido</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06/03/2026 23:26</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>410</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Martinez</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>4004004004004</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MASTERCARD - Pago Registrada</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>$55.000/TC 1420/MASTER 5678/CUPON 8803/LOTE 100</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1.420,09</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>$ 55.000,00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1-1004</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>✅ Pago parcial 2/2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>RES-10046</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Fernández, Laura</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>FA-0001-00010046</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>98500</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>102000</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>-3500</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>VERIFICAR TIPEO</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Diferencia $3.500 — posible retención IIBB</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>06/03/2026 23:30</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>118</v>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>5005005005005</v>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>VISA_CREDITO - Pago Registrada</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>$60.000/TC 1420/VISA 9012/CUPON 8804/LOTE 100</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>1.420,12</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>$ 60.000,00</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>❌ No se encontró factura</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>FX-0001-00010099</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06/03/2026 23:31</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pedro</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Gomez</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>5005005005005</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VOID - anulación de pago</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>55000</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>-55000</v>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>SIN MATCH</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Factura SF sin contrapartida en CloudBeds</t>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⚪ Anulación registrada (sin Nota de Crédito asociada en SF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>06/03/2026 23:40</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>507</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Fernandez</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>6006006006006</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>TRANSFERENCIA - Pago Registrada</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>$98.500 TC 1420 TRANSFERENCIA EMPRESA XYZ</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1.419,92</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>$ 98.500,00</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1-1006</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ REVISAR DISCREPANCIA: CB ($98,500.00) ↔ SF ($102,000.00)</t>
         </is>
       </c>
     </row>
